--- a/artfynd/A 21612-2021 artfynd.xlsx
+++ b/artfynd/A 21612-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130149889</v>
       </c>
       <c r="B2" t="n">
-        <v>58461</v>
+        <v>58546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>130149739</v>
       </c>
       <c r="B3" t="n">
-        <v>58421</v>
+        <v>58506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21612-2021 artfynd.xlsx
+++ b/artfynd/A 21612-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130149889</v>
       </c>
       <c r="B2" t="n">
-        <v>58546</v>
+        <v>58572</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>130149739</v>
       </c>
       <c r="B3" t="n">
-        <v>58506</v>
+        <v>58532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
